--- a/Time sheet for the month of Sep'26.xlsx
+++ b/Time sheet for the month of Sep'26.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1edcdba9229180ce/Desktop/Timesheet/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amdocs-my.sharepoint.com/personal/tuusharv_amdocs_com/Documents/Desktop/01_Time_Zone/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="451" documentId="13_ncr:1_{B0658610-58E3-4C61-BD07-86C2132128FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64F05824-9BE6-4935-97BF-B41157BED379}"/>
+  <xr:revisionPtr revIDLastSave="467" documentId="13_ncr:1_{B0658610-58E3-4C61-BD07-86C2132128FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C37ED3AD-2D52-4A38-9AC7-E43EB841FE55}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="36">
   <si>
     <t>*  Please fill the below details of name, Client Name, Project Mgr,EMP ID</t>
   </si>
@@ -127,17 +127,28 @@
   </si>
   <si>
     <t>TIMESHEET FOR THE MONTH OF SEP 2026</t>
+  </si>
+  <si>
+    <t>Tuushar V Kalokkhe</t>
+  </si>
+  <si>
+    <t>AMDOCS</t>
+  </si>
+  <si>
+    <t>USCC</t>
+  </si>
+  <si>
+    <t>Hagit Rejiniano, Rahul Salve</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d\-mmm\-yyyy"/>
-    <numFmt numFmtId="165" formatCode="[$-409]d/mmm/yy"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -171,18 +182,13 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -209,12 +215,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor rgb="FF8496B0"/>
       </patternFill>
@@ -494,7 +494,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
@@ -516,25 +516,22 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -554,9 +551,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -565,13 +559,13 @@
     <xf numFmtId="17" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -589,10 +583,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -891,45 +881,49 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AD102"/>
-  <sheetFormatPr defaultColWidth="14.46484375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="30" width="4.6640625" customWidth="1"/>
+    <col min="1" max="7" width="4.6328125" customWidth="1"/>
+    <col min="8" max="8" width="5.453125" customWidth="1"/>
+    <col min="9" max="10" width="4.6328125" customWidth="1"/>
+    <col min="11" max="11" width="6" customWidth="1"/>
+    <col min="12" max="30" width="4.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="21"/>
-      <c r="R1" s="21"/>
-      <c r="S1" s="21"/>
-      <c r="T1" s="21"/>
-      <c r="U1" s="21"/>
-      <c r="V1" s="21"/>
-      <c r="W1" s="22"/>
-    </row>
-    <row r="2" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="21"/>
+    </row>
+    <row r="2" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="W2" s="2"/>
     </row>
-    <row r="3" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -956,132 +950,136 @@
       <c r="V3" s="4"/>
       <c r="W3" s="5"/>
     </row>
-    <row r="4" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="5" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="23" t="s">
+    <row r="4" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="31">
+      <c r="B5" s="23"/>
+      <c r="C5" s="29">
         <v>2026</v>
       </c>
-      <c r="D5" s="32"/>
-    </row>
-    <row r="6" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="25" t="s">
+      <c r="D5" s="30"/>
+    </row>
+    <row r="6" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="26"/>
-      <c r="C6" s="33">
+      <c r="B6" s="25"/>
+      <c r="C6" s="31">
         <v>46266</v>
       </c>
-      <c r="D6" s="30"/>
+      <c r="D6" s="28"/>
       <c r="F6" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="27"/>
-      <c r="H6" s="28"/>
+      <c r="G6" s="26">
+        <v>45824</v>
+      </c>
+      <c r="H6" s="27"/>
       <c r="I6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="J6" s="29"/>
-      <c r="K6" s="30"/>
-    </row>
-    <row r="7" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="8" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="9" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="14" t="s">
+      <c r="J6" s="26">
+        <v>46295</v>
+      </c>
+      <c r="K6" s="27"/>
+    </row>
+    <row r="7" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="8" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="9" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="G9" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="H9" s="14" t="s">
+      <c r="H9" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="I9" s="14" t="s">
+      <c r="I9" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="J9" s="14" t="s">
+      <c r="J9" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="K9" s="14" t="s">
+      <c r="K9" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="L9" s="15" t="s">
+      <c r="L9" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="M9" s="15" t="s">
+      <c r="M9" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="N9" s="14" t="s">
+      <c r="N9" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="O9" s="14" t="s">
+      <c r="O9" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="P9" s="14" t="s">
+      <c r="P9" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="Q9" s="14" t="s">
+      <c r="Q9" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="R9" s="14" t="s">
+      <c r="R9" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="S9" s="15" t="s">
+      <c r="S9" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="T9" s="15" t="s">
+      <c r="T9" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="U9" s="14" t="s">
+      <c r="U9" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="V9" s="14" t="s">
+      <c r="V9" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="W9" s="14" t="s">
+      <c r="W9" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="X9" s="14" t="s">
+      <c r="X9" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="Y9" s="14" t="s">
+      <c r="Y9" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="Z9" s="15" t="s">
+      <c r="Z9" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="AA9" s="15" t="s">
+      <c r="AA9" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="AB9" s="14" t="s">
+      <c r="AB9" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="AC9" s="14" t="s">
+      <c r="AC9" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AD9" s="14" t="s">
+      <c r="AD9" s="13" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="12">
         <v>1</v>
       </c>
@@ -1173,39 +1171,99 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
-      <c r="P11" s="13"/>
-      <c r="Q11" s="13"/>
-      <c r="R11" s="13"/>
-      <c r="S11" s="13"/>
-      <c r="T11" s="13"/>
-      <c r="U11" s="13"/>
-      <c r="V11" s="13"/>
-      <c r="W11" s="13"/>
-      <c r="X11" s="13"/>
-      <c r="Y11" s="13"/>
-      <c r="Z11" s="13"/>
-      <c r="AA11" s="13"/>
-      <c r="AB11" s="13"/>
-      <c r="AC11" s="13"/>
-      <c r="AD11" s="13"/>
-    </row>
-    <row r="12" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="N11" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="O11" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="P11" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q11" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="R11" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="S11" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="T11" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="U11" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="V11" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="W11" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="X11" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y11" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="Z11" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA11" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB11" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="AC11" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD11" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
@@ -1237,7 +1295,7 @@
       <c r="AC12" s="10"/>
       <c r="AD12" s="10"/>
     </row>
-    <row r="13" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -1269,21 +1327,23 @@
       <c r="AC13" s="8"/>
       <c r="AD13" s="8"/>
     </row>
-    <row r="14" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="15" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="34" t="s">
+    <row r="14" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="15" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="35"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="18"/>
-      <c r="K15" s="19"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="33"/>
+      <c r="J15" s="33"/>
+      <c r="K15" s="34"/>
       <c r="P15" t="s">
         <v>13</v>
       </c>
@@ -1291,20 +1351,22 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="34" t="s">
+    <row r="16" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="35"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="36"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="18"/>
-      <c r="K16" s="19"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="34"/>
       <c r="P16" t="s">
         <v>17</v>
       </c>
@@ -1312,41 +1374,45 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="34" t="s">
+    <row r="17" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="35"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="18"/>
-      <c r="K17" s="19"/>
-      <c r="P17" s="16">
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17" s="33"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="33"/>
+      <c r="J17" s="33"/>
+      <c r="K17" s="34"/>
+      <c r="P17" s="15">
         <v>0.5</v>
       </c>
       <c r="Q17" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="34" t="s">
+    <row r="18" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="36"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="18"/>
-      <c r="K18" s="19"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="33"/>
+      <c r="K18" s="34"/>
       <c r="P18" t="s">
         <v>28</v>
       </c>
@@ -1354,20 +1420,22 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="34" t="s">
+    <row r="19" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="35"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="18"/>
-      <c r="J19" s="18"/>
-      <c r="K19" s="19"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="32">
+        <v>210517</v>
+      </c>
+      <c r="G19" s="33"/>
+      <c r="H19" s="33"/>
+      <c r="I19" s="33"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="34"/>
       <c r="P19" t="s">
         <v>22</v>
       </c>
@@ -1375,7 +1443,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="P20" t="s">
         <v>25</v>
       </c>
@@ -1383,7 +1451,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="P21" t="s">
         <v>20</v>
       </c>
@@ -1391,97 +1459,89 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="23" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="24" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="25" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="26" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="27" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="28" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="29" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="30" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="31" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="32" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="33" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="34" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="35" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="36" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="37" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="38" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="39" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="40" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="41" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="42" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="43" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="44" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="45" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="46" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="47" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="48" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="49" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="50" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="51" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="52" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="53" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="54" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="55" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="56" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="57" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="58" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="59" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="60" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="61" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="62" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="63" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="64" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="65" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="66" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="67" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="68" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="69" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="70" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="71" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="72" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="75" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="76" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="77" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="78" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="79" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="80" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="81" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="82" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="83" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="84" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="85" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="86" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="87" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="88" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="89" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="90" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="91" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="92" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="93" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="94" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="95" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="96" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="97" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="98" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="99" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="100" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="101" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="102" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="22" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="23" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="24" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="25" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="26" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="27" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="28" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="29" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="30" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="31" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="32" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="33" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="35" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="36" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="37" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="39" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="40" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="41" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="42" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="43" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="44" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="45" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="46" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="47" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="48" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="49" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="50" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="51" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="52" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="53" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="54" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="55" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="56" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="57" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="58" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="59" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="60" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="61" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="62" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="63" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="64" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="65" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="66" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="67" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="68" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="69" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="70" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="71" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="72" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="75" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="76" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="77" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="78" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="79" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="80" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="81" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="82" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="83" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="84" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="85" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="86" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="87" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="88" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="89" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="90" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="91" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="92" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="93" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="94" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="95" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="96" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="97" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="98" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="99" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="100" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="101" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="102" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="F16:K16"/>
-    <mergeCell ref="F19:K19"/>
-    <mergeCell ref="F17:K17"/>
-    <mergeCell ref="F18:K18"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
     <mergeCell ref="F15:K15"/>
     <mergeCell ref="A1:W1"/>
     <mergeCell ref="A5:B5"/>
@@ -1491,9 +1551,23 @@
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="F16:K16"/>
+    <mergeCell ref="F19:K19"/>
+    <mergeCell ref="F17:K17"/>
+    <mergeCell ref="F18:K18"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A18:E18"/>
   </mergeCells>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{c8eca3ca-1276-46d5-9d9d-a0f2a028920f}" enabled="0" method="" siteId="{c8eca3ca-1276-46d5-9d9d-a0f2a028920f}" removed="1"/>
+</clbl:labelList>
 </file>